--- a/assessment_forms/037_tech_industry_candidate_skills_interview_form--assessment_forms.xlsx
+++ b/assessment_forms/037_tech_industry_candidate_skills_interview_form--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1137,8 +1137,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'python',_'label':_'python'}</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'python', 'label': 'Python'}</t>
+          <t>Python</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'java',_'label':_'java'}</t>
+          <t>java</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'java', 'label': 'Java'}</t>
+          <t>Java</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_30,_'name':_'csharp',_'label':_'c#'}</t>
+          <t>c#</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 30, 'name': 'csharp', 'label': 'C#'}</t>
+          <t>C#</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'problem_solving',_'label':_'problem_solving'}</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'problem_solving', 'label': 'Problem Solving'}</t>
+          <t>Problem Solving</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'communication',_'label':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'communication', 'label': 'Communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_31,_'name':_'leadership',_'label':_'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 31, 'name': 'leadership', 'label': 'Leadership'}</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'high_school',_'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'high_school', 'label': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'bachelor',_'label':_'bachelor'}</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'bachelor', 'label': 'Bachelor'}</t>
+          <t>Bachelor</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_32,_'name':_'master',_'label':_'master'}</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 32, 'name': 'master', 'label': 'Master'}</t>
+          <t>Master</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'english',_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'english', 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'french',_'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'french', 'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_33,_'name':_'spanish',_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 33, 'name': 'spanish', 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'aws',_'label':_'aws'}</t>
+          <t>aws</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'aws', 'label': 'AWS'}</t>
+          <t>AWS</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'azure',_'label':_'azure'}</t>
+          <t>azure</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'azure', 'label': 'Azure'}</t>
+          <t>Azure</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_34,_'name':_'oracle',_'label':_'oracle'}</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 34, 'name': 'oracle', 'label': 'Oracle'}</t>
+          <t>Oracle</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'usa',_'label':_'usa'}</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'usa', 'label': 'USA'}</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'canada',_'label':_'canada'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': 'canada', 'label': 'Canada'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_35,_'name':_'australia',_'label':_'australia'}</t>
+          <t>australia</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 35, 'name': 'australia', 'label': 'Australia'}</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_26,_'name':_'linkedin',_'label':_'linkedin'}</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 26, 'name': 'linkedin', 'label': 'LinkedIn'}</t>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_27,_'name':_'instagram',_'label':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 27, 'name': 'instagram', 'label': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_28,_'name':_'github',_'label':_'github'}</t>
+          <t>github</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 28, 'name': 'github', 'label': 'GitHub'}</t>
+          <t>GitHub</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_36,_'name':_'schedule_next_interview',_'label':_'schedule_next_interview'}</t>
+          <t>schedule_next_interview</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 36, 'name': 'schedule_next_interview', 'label': 'Schedule next interview'}</t>
+          <t>Schedule next interview</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_37,_'name':_'move_to_next_round',_'label':_'move_to_next_round'}</t>
+          <t>move_to_next_round</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 37, 'name': 'move_to_next_round', 'label': 'Move to next round'}</t>
+          <t>Move to next round</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_38,_'name':_'decline_candidate',_'label':_'decline_candidate'}</t>
+          <t>decline_candidate</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 38, 'name': 'decline_candidate', 'label': 'Decline candidate'}</t>
+          <t>Decline candidate</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_29,_'name':_'send_email',_'label':_'send_email'}</t>
+          <t>send_email</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 29, 'name': 'send_email', 'label': 'Send email'}</t>
+          <t>Send email</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1591,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_40,_'name':_'call',_'label':_'call'}</t>
+          <t>call</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 40, 'name': 'call', 'label': 'Call'}</t>
+          <t>Call</t>
         </is>
       </c>
     </row>
